--- a/frontend/inventaire produits pharmaceutiques2024.xlsx
+++ b/frontend/inventaire produits pharmaceutiques2024.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Direction Régionale </t>
   </si>
   <si>
-    <t>Gasii Touil</t>
+    <t>Gassi Touil</t>
   </si>
   <si>
     <t>Division Personnel</t>
